--- a/artfynd/A 27469-2026 artfynd.xlsx
+++ b/artfynd/A 27469-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86351474</v>
+        <v>86351471</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>219955</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,17 +703,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Salebo, Långrödjan, 225 m VNV, Ög</t>
+          <t>Salebo, Långrödjan, 155 m NV, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508061.3763296796</v>
+        <v>508135</v>
       </c>
       <c r="R2" t="n">
-        <v>6401606.576154415</v>
+        <v>6401590</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +755,14 @@
           <t>2020-06-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5 stäbglar i knopp och blom</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,12 +798,7 @@
         <v>86351475</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508061.3763296796</v>
+        <v>508061</v>
       </c>
       <c r="R3" t="n">
-        <v>6401606.576154415</v>
+        <v>6401607</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +863,9 @@
           <t>2020-06-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,32 +897,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86351471</v>
+        <v>86351474</v>
       </c>
       <c r="B4" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219955</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,29 +925,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Salebo, Långrödjan, 155 m NV, Ög</t>
+          <t>Salebo, Långrödjan, 225 m VNV, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508134.6480455798</v>
+        <v>508061</v>
       </c>
       <c r="R4" t="n">
-        <v>6401590.1827902</v>
+        <v>6401607</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,24 +965,9 @@
           <t>2020-06-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5 stäbglar i knopp och blom</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +976,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1041,146 +996,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>97299737</v>
-      </c>
-      <c r="B5" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>219955</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Slåttergubbe</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Arnica montana</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Salebo, Långrödjan, 155 m NV, Ög</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>508135.7172227988</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6401590.18494777</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Ydre</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Västra Ryd</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>E-Ydr-0117</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>5 stänglar i knopp och blom</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>ängsrest i vägkant</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Monika Sunhede</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anders Svenson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27469-2026 artfynd.xlsx
+++ b/artfynd/A 27469-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86351471</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86351475</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86351474</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>